--- a/AAII_Financials/Quarterly/PINXY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PINXY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
   <si>
     <t>PINXY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,58 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -735,8 +741,14 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -764,8 +776,14 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -793,8 +811,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -806,8 +830,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -835,8 +861,14 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -864,8 +896,14 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -893,8 +931,14 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -922,8 +966,14 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -932,8 +982,10 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -961,8 +1013,14 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -990,8 +1048,14 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1003,8 +1067,10 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1032,8 +1098,14 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1061,8 +1133,14 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1090,8 +1168,14 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1119,8 +1203,14 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1148,8 +1238,14 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1177,8 +1273,14 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1206,8 +1308,14 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1235,8 +1343,14 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1264,8 +1378,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1293,8 +1413,14 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1322,8 +1448,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1351,8 +1483,14 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1380,8 +1518,14 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1409,8 +1553,14 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1438,8 +1588,14 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1467,42 +1623,54 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1514,8 +1682,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1527,95 +1697,115 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4473800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3411700</v>
+      </c>
+      <c r="F41" s="3">
         <v>2864600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2946600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2802400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2875900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2730300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2281100</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M41" s="3">
         <v>3097600</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>47302300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>46156400</v>
+      </c>
+      <c r="F42" s="3">
         <v>49854600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>47181200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>54320900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>55206300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1103300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>52909600</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>8341800</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>89400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>830500</v>
+      </c>
+      <c r="F43" s="3">
         <v>215000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>429200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>239200</v>
       </c>
-      <c r="G43" s="3">
-        <v>1567100</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>525900</v>
+      </c>
+      <c r="J43" s="3">
         <v>121300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>257300</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3">
         <v>1702300</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1643,153 +1833,189 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4791300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>7756300</v>
+      </c>
+      <c r="F45" s="3">
         <v>5288600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>7002800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>4790700</v>
       </c>
-      <c r="G45" s="3">
-        <v>7610700</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>8095600</v>
+      </c>
+      <c r="J45" s="3">
         <v>4607400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>5953800</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>7965300</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>58546500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>60261400</v>
+      </c>
+      <c r="F46" s="3">
         <v>60631300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>59701500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>64064100</v>
       </c>
-      <c r="G46" s="3">
-        <v>69273200</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
+        <v>68716800</v>
+      </c>
+      <c r="J46" s="3">
         <v>10408300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>63251900</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M46" s="3">
         <v>23065300</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>176407500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>171248800</v>
+      </c>
+      <c r="F47" s="3">
         <v>167803400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>156323700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>140598400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>139899700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>182911600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>131012100</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3">
         <v>171007100</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4729100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5508200</v>
+      </c>
+      <c r="F48" s="3">
         <v>4904100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4714100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>4755100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>5613000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>4748200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>5530100</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="3">
         <v>5979100</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1119000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>465800</v>
+      </c>
+      <c r="F49" s="3">
         <v>1106300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1129100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1128900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>527700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1064300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>438200</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>539500</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1817,8 +2043,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1846,37 +2078,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5234900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2744600</v>
+      </c>
+      <c r="F52" s="3">
         <v>5984700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2754300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>5655400</v>
       </c>
-      <c r="G52" s="3">
-        <v>2226900</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
+        <v>2783300</v>
+      </c>
+      <c r="J52" s="3">
         <v>4830100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3098500</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3">
         <v>2187100</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1904,37 +2148,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>248121000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>241991600</v>
+      </c>
+      <c r="F54" s="3">
         <v>242569700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>227151600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>218067700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>219532400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>206497100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>205821500</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M54" s="3">
         <v>205342300</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1946,8 +2202,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1959,182 +2217,220 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>33986200</v>
+      </c>
+      <c r="F57" s="3">
         <v>26800</v>
       </c>
-      <c r="E57" s="3">
-        <v>822200</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
+        <v>246900</v>
+      </c>
+      <c r="H57" s="3">
         <v>20900</v>
       </c>
-      <c r="G57" s="3">
-        <v>706100</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>32403600</v>
+      </c>
+      <c r="J57" s="3">
         <v>24900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>842900</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3">
         <v>821900</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16811500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>15330500</v>
+      </c>
+      <c r="F58" s="3">
         <v>15443700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>12772300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>10182400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>15479000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>12938200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>11200300</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>14741800</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1721600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1744600</v>
+      </c>
+      <c r="F59" s="3">
         <v>2709200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3460600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1634500</v>
       </c>
-      <c r="G59" s="3">
-        <v>1449900</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>873200</v>
+      </c>
+      <c r="J59" s="3">
         <v>975500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2295300</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>1263300</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23641600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>56846600</v>
+      </c>
+      <c r="F60" s="3">
         <v>22961200</v>
       </c>
-      <c r="E60" s="3">
-        <v>22132700</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>21557300</v>
+      </c>
+      <c r="H60" s="3">
         <v>16340800</v>
       </c>
-      <c r="G60" s="3">
-        <v>23125000</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>54245900</v>
+      </c>
+      <c r="J60" s="3">
         <v>19603800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>19221200</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M60" s="3">
         <v>22034700</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6076300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7115800</v>
+      </c>
+      <c r="F61" s="3">
         <v>5722900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>5460700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>5573300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>5651500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>5511100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>5600200</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>6583500</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>165702500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>127244900</v>
+      </c>
+      <c r="F62" s="3">
         <v>161754200</v>
       </c>
-      <c r="E62" s="3">
-        <v>151526000</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
+        <v>152101300</v>
+      </c>
+      <c r="H62" s="3">
         <v>149457500</v>
       </c>
-      <c r="G62" s="3">
-        <v>143367700</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>112246800</v>
+      </c>
+      <c r="J62" s="3">
         <v>136694400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>135083800</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>131823100</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2162,8 +2458,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2191,8 +2493,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2220,37 +2528,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>195519300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>191653800</v>
+      </c>
+      <c r="F66" s="3">
         <v>190502800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>179572300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>171398000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>172584400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>161859900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>160288000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M66" s="3">
         <v>161137000</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2262,8 +2582,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2291,8 +2613,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2320,8 +2648,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2349,8 +2683,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2378,37 +2718,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>33268200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>24391100</v>
+      </c>
+      <c r="F72" s="3">
         <v>31376100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>28382800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>27564400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>24254000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>25740300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>24147600</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>24327000</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2436,8 +2788,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2465,8 +2823,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2494,37 +2858,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38496000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>36835500</v>
+      </c>
+      <c r="F76" s="3">
         <v>38158200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>34818100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>34045100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>34298300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>32952300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>33611800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>32631600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>32499100</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2552,42 +2928,54 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2615,8 +3003,14 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2628,37 +3022,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3">
+        <v>538700</v>
+      </c>
+      <c r="F83" s="3">
         <v>-342100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>245700</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3">
         <v>601000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>-349200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>185400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>195900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>629000</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2686,8 +3088,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2715,8 +3123,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2744,8 +3158,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2773,8 +3193,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2802,37 +3228,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5036700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>956100</v>
+      </c>
+      <c r="F89" s="3">
         <v>1563500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>5076400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>4591600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>953300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>530100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2579600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>5999700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>2746300</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2844,37 +3282,45 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-438100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-60300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-60700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-46400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-347800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-35600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-57500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-62600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-701700</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2902,8 +3348,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2931,37 +3383,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5529100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1229700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3445700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-6847300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>734900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-2763000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1430000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-4995500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-680100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-3723700</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2973,37 +3437,45 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>535800</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3">
         <v>1475400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>150700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>127000</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
         <v>1505400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>344600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>43800</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3031,8 +3503,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3060,8 +3538,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3089,91 +3573,115 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>3001600</v>
+      </c>
+      <c r="F100" s="3">
         <v>671500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>2451800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-5481100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>2210400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>213500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>2430000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-6745800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>3090400</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-23700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>37500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-2500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-117100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>121000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>25900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>27400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-23600</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-500400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2777900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1238300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>663400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-154300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>402900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-710100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>51600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1428700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1995900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PINXY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PINXY_QTR_FIN.xlsx
@@ -2491,7 +2491,7 @@
         <v>200600</v>
       </c>
       <c r="F57" s="3">
-        <v>19000</v>
+        <v>1088000</v>
       </c>
       <c r="G57" s="3">
         <v>33986200</v>
@@ -2614,7 +2614,7 @@
         <v>26244600</v>
       </c>
       <c r="F60" s="3">
-        <v>23641600</v>
+        <v>24710500</v>
       </c>
       <c r="G60" s="3">
         <v>56846600</v>
@@ -2696,7 +2696,7 @@
         <v>174999200</v>
       </c>
       <c r="F62" s="3">
-        <v>165702500</v>
+        <v>164633500</v>
       </c>
       <c r="G62" s="3">
         <v>127244900</v>

--- a/AAII_Financials/Quarterly/PINXY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PINXY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="92">
   <si>
     <t>PINXY</t>
   </si>
@@ -656,70 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -759,8 +765,14 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -800,8 +812,14 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -841,8 +859,14 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -858,8 +882,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -899,8 +925,14 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -940,8 +972,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -981,8 +1019,14 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1022,8 +1066,14 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1036,8 +1086,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1077,8 +1129,14 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1118,8 +1176,14 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1135,8 +1199,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1176,8 +1242,14 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1217,8 +1289,14 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1258,8 +1336,14 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1299,8 +1383,14 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1340,8 +1430,14 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1381,8 +1477,14 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1422,8 +1524,14 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1463,8 +1571,14 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1504,8 +1618,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1545,8 +1665,14 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1586,8 +1712,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1627,8 +1759,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1668,8 +1806,14 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1709,8 +1853,14 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1750,8 +1900,14 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1791,54 +1947,66 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1854,8 +2022,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1871,131 +2041,151 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3664700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3472300</v>
+      </c>
+      <c r="F41" s="3">
         <v>3281100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3197500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4473800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3411700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2864600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2946600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2802400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2875900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2730300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2281100</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q41" s="3">
         <v>3097600</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>62919800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>63665800</v>
+      </c>
+      <c r="F42" s="3">
         <v>56706800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>52153900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>47302300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>46156400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>49854600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>47181200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>54320900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>55206300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1103300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>52909600</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>8341800</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>79500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>664500</v>
+      </c>
+      <c r="F43" s="3">
         <v>119000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>869200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>89400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>830500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>215000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>429200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>239200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>525900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>121300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>257300</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="3">
         <v>1702300</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2035,213 +2225,249 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5412500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>8362500</v>
+      </c>
+      <c r="F45" s="3">
         <v>5044900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>6808400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>4791300</v>
       </c>
-      <c r="G45" s="3">
-        <v>7756300</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>7831200</v>
+      </c>
+      <c r="J45" s="3">
         <v>5288600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>7002800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>4790700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>8095600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>4607400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>5953800</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>7965300</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>74055900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>78235300</v>
+      </c>
+      <c r="F46" s="3">
         <v>67078300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>65165000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>58546500</v>
       </c>
-      <c r="G46" s="3">
-        <v>60261400</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
+        <v>60336300</v>
+      </c>
+      <c r="J46" s="3">
         <v>60631300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>59701500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>64064100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>68716800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>10408300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>63251900</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q46" s="3">
         <v>23065300</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>205606500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>200672000</v>
+      </c>
+      <c r="F47" s="3">
         <v>192486800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>185984500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>176407500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>171248800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>167803400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>156323700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>140598400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>139899700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>182911600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>131012100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="3">
         <v>171007100</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4915000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5636700</v>
+      </c>
+      <c r="F48" s="3">
         <v>4622400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4600800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>4729100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>5508200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>4904100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4714100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4755100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>5613000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4748200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>5530100</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q48" s="3">
         <v>5979100</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1189600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>536000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1040400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1075000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1119000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>465800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1106300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1129100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1128900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>527700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1064300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>438200</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
         <v>539500</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2281,8 +2507,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2322,49 +2554,61 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5388000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2749900</v>
+      </c>
+      <c r="F52" s="3">
         <v>5476900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2861200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>5234900</v>
       </c>
-      <c r="G52" s="3">
-        <v>2744600</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
+        <v>2669600</v>
+      </c>
+      <c r="J52" s="3">
         <v>5984700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2754300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>5655400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2783300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>4830100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3098500</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="3">
         <v>2187100</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2404,49 +2648,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>293373600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>289887900</v>
+      </c>
+      <c r="F54" s="3">
         <v>272927700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>262220500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>248121000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>241991600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>242569700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>227151600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>218067700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>219532400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>206497100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>205821500</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q54" s="3">
         <v>205342300</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2462,8 +2718,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2479,254 +2737,292 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>21900</v>
+        <v>937900</v>
       </c>
       <c r="E57" s="3">
-        <v>200600</v>
+        <v>38350400</v>
       </c>
       <c r="F57" s="3">
+        <v>1112600</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1250600</v>
+      </c>
+      <c r="H57" s="3">
         <v>1088000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>33986200</v>
       </c>
-      <c r="H57" s="3">
-        <v>26800</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
+        <v>1175000</v>
+      </c>
+      <c r="K57" s="3">
         <v>246900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>20900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>32403600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>24900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>842900</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="3">
         <v>821900</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>22168400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>25944800</v>
+      </c>
+      <c r="F58" s="3">
         <v>16663200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>14560600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>16811500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>15330500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>15443700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>12772300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>10182400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>15479000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>12938200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>11200300</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>14741800</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1696100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2062400</v>
+      </c>
+      <c r="F59" s="3">
         <v>2350700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>5582500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1721600</v>
       </c>
-      <c r="G59" s="3">
-        <v>1744600</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>1434300</v>
+      </c>
+      <c r="J59" s="3">
         <v>2709200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>3460600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1634500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>873200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>975500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2295300</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>1263300</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>24399400</v>
+        <v>30571100</v>
       </c>
       <c r="E60" s="3">
-        <v>26244600</v>
+        <v>72756100</v>
       </c>
       <c r="F60" s="3">
+        <v>25490100</v>
+      </c>
+      <c r="G60" s="3">
+        <v>27294600</v>
+      </c>
+      <c r="H60" s="3">
         <v>24710500</v>
       </c>
-      <c r="G60" s="3">
-        <v>56846600</v>
-      </c>
-      <c r="H60" s="3">
-        <v>22961200</v>
-      </c>
       <c r="I60" s="3">
+        <v>56536300</v>
+      </c>
+      <c r="J60" s="3">
+        <v>24109300</v>
+      </c>
+      <c r="K60" s="3">
         <v>21557300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>16340800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>54245900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>19603800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>19221200</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q60" s="3">
         <v>22034700</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6399700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6187700</v>
+      </c>
+      <c r="F61" s="3">
         <v>6170400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>6079600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>6076300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>7115800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>5722900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>5460700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>5573300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>5651500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>5511100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>5600200</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>6583500</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>181985100</v>
+        <v>193270900</v>
       </c>
       <c r="E62" s="3">
-        <v>174999200</v>
+        <v>150263400</v>
       </c>
       <c r="F62" s="3">
+        <v>180894300</v>
+      </c>
+      <c r="G62" s="3">
+        <v>173949200</v>
+      </c>
+      <c r="H62" s="3">
         <v>164633500</v>
       </c>
-      <c r="G62" s="3">
-        <v>127244900</v>
-      </c>
-      <c r="H62" s="3">
-        <v>161754200</v>
-      </c>
       <c r="I62" s="3">
+        <v>127555200</v>
+      </c>
+      <c r="J62" s="3">
+        <v>160606000</v>
+      </c>
+      <c r="K62" s="3">
         <v>152101300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>149457500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>112246800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>136694400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>135083800</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3">
         <v>131823100</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2766,8 +3062,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2807,8 +3109,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2848,49 +3156,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>230419600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>229773200</v>
+      </c>
+      <c r="F66" s="3">
         <v>212831600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>207856000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>195519300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>191653800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>190502800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>179572300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>171398000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>172584400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>161859900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>160288000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q66" s="3">
         <v>161137000</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2906,8 +3226,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2947,8 +3269,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2988,8 +3316,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3029,8 +3363,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3070,49 +3410,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>40367200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>32984200</v>
+      </c>
+      <c r="F72" s="3">
         <v>38023500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>34914800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>33268200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>24391100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>31376100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>28382800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>27564400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>24254000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>25740300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>24147600</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3">
         <v>24327000</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3152,8 +3504,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3193,8 +3551,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3234,49 +3598,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>46300900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>44204400</v>
+      </c>
+      <c r="F76" s="3">
         <v>44116100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>39798800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>38496000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>36835500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>38158200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>34818100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>34045100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>34298300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>32952300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>33611800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>32631600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>32499100</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3316,54 +3692,66 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3403,8 +3791,14 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3420,49 +3814,57 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3">
+        <v>489100</v>
+      </c>
+      <c r="F83" s="3">
         <v>-344100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>332200</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3">
         <v>538700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>-342100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>245700</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3">
         <v>601000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>-349200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>185400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>195900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>629000</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3502,8 +3904,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3543,8 +3951,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3584,8 +3998,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3625,8 +4045,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3666,49 +4092,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2225500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>3273000</v>
+      </c>
+      <c r="F89" s="3">
         <v>2942900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>5345800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>5036700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>956100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1563500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>5076400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>4591600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>953300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>530100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2579600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>5999700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2746300</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3724,49 +4162,57 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-538700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-49900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-74000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-18100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-438100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-60300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-60700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-46400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-347800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-35600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-57500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-62600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-701700</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3806,8 +4252,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3847,49 +4299,61 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1053000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-7687100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-5091000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-3575100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-5529100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1229700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-3445700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-6847300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>734900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-2763000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1430000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-4995500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-680100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-3723700</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3905,49 +4369,57 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>389000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>921300</v>
+      </c>
+      <c r="F96" s="3">
         <v>289800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>126500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>535800</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
         <v>1475400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>150700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>127000</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
         <v>1505400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>344600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>43800</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3987,8 +4459,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4028,8 +4506,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4069,127 +4553,151 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4435000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>7577300</v>
+      </c>
+      <c r="F100" s="3">
         <v>2100400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-2025900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-7400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>3001600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>671500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>2451800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-5481100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>2210400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>213500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>2430000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-6745800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>3090400</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>49900</v>
+      </c>
+      <c r="F101" s="3">
         <v>-27500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-17500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>2100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-23700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>37500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-2500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-117100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>121000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>25900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>27400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-23600</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3286600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>3092200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-39000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-276000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-500400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>2777900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1238300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>663400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-154300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>402900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-710100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>51600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1428700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1995900</v>
       </c>
     </row>
